--- a/data/trending_integrated_20261023_12.xlsx
+++ b/data/trending_integrated_20261023_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4215</v>
+        <v>4262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.40%</t>
+          <t>'+13.65%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F2" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G2" t="n">
-        <v>496</v>
+        <v>513</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>133766458819</v>
+        <v>135354138492</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 이상 징후와 연계된 방산주 급등. 외인 매도세 및 전쟁 불안감.</t>
+          <t>북한 관련 지정학적 리스크 부각으로 인한 방산주 동반 상승 기대. 미국 시장 급등 및 코브라볼 평택 포착 등 뉴스 기반 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['방산주', '북한', '외인']</t>
+          <t>['지정학적 리스크', '방산주', '코브라볼']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60400</v>
+        <v>60300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.03%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F3" t="n">
         <v>164</v>
       </c>
       <c r="G3" t="n">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>538283688350</v>
+        <v>542269234600</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관의 대규모 자사주 매입 및 매각 자금 유입, MSCI 패시브 자금 유입 전망에 따른 주가 상승 기대감.</t>
+          <t>외국인 및 기관 매수세 유입, 자사주 매입/소각 공시, MSCI 편입 기대감으로 인한 상승 전망. 중동 특수 및 과거 주가 흐름 기반 목표가 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI 패시브']</t>
+          <t>['자사주 매입', 'MSCI 편입', '중동 특수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1228000</v>
+        <v>1222000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'-0.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G4" t="n">
-        <v>1285</v>
+        <v>1307</v>
       </c>
       <c r="H4" t="n">
         <v>48.77</v>
@@ -794,7 +794,7 @@
         <v>48.79</v>
       </c>
       <c r="O4" t="n">
-        <v>2333791894000</v>
+        <v>2365660076000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주주환원 발표 기대감 속 기관 매도세 관찰. 솔리다임 IPO 중단 이슈.</t>
+          <t>매도 의견과 함께 부정적 언급이 많으나, 주주환원 발표 기대감 및 일부 투자자의 매수 의견 존재. 나스닥 반도체 하락 영향 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주주환원', 'IPO', '기관']</t>
+          <t>['주주환원', '매도 의견', '나스닥 하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,21 +843,21 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8710</v>
+        <v>8650</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
         <v>178</v>
@@ -886,7 +886,7 @@
         <v>5.15</v>
       </c>
       <c r="O5" t="n">
-        <v>6141928850</v>
+        <v>6243927810</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13360</v>
+        <v>13250</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.15%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>51530706235</v>
+        <v>52340364325</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>EUV 유리기판 관련 기술성 부각, 삼성 인수설 및 외인 매수세 유입, SK하이닉스 반등에 따른 기대감.</t>
+          <t>유리기판 관련 기술성 부각 및 삼성 인수설 기반 긍정적 전망. 외인 매수세 유입 및 SK하이닉스 반등에 따른 상승 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', 'EUV', '외인 매수']</t>
+          <t>['유리기판', '삼성 인수설', '외인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,184 +1023,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17290</v>
+        <v>14380</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-1.03%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>3.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17350</v>
+        <v>14530</v>
       </c>
       <c r="K7" t="n">
-        <v>18130</v>
+        <v>14190</v>
       </c>
       <c r="L7" t="n">
-        <v>19070</v>
+        <v>14710</v>
       </c>
       <c r="M7" t="n">
-        <v>16530</v>
+        <v>13810</v>
       </c>
       <c r="N7" t="n">
-        <v>3.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>46165909775</v>
+        <v>22081255820</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>-11000</v>
+        <v>-96000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등 속 라온시큐어 주가 변동성. AI 보안 해킹 우려.</t>
+          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '해킹']</t>
+          <t>['실적 발표', '공매도', '주가 조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14430</v>
+        <v>17020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.69%</t>
+          <t>'-1.90%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
         <v>139</v>
       </c>
       <c r="H8" t="n">
-        <v>9.890000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14530</v>
+        <v>17350</v>
       </c>
       <c r="K8" t="n">
-        <v>14190</v>
+        <v>18130</v>
       </c>
       <c r="L8" t="n">
-        <v>14710</v>
+        <v>19070</v>
       </c>
       <c r="M8" t="n">
-        <v>13810</v>
+        <v>16530</v>
       </c>
       <c r="N8" t="n">
-        <v>9.949999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>21766106060</v>
+        <v>46510245965</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>6320</v>
       </c>
       <c r="R8" t="n">
-        <v>-96000</v>
+        <v>-11000</v>
       </c>
       <c r="S8" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
+          <t>미국 보안주 폭등 속 라온시큐어 주가 변동성. AI 보안 해킹 우려.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['실적 발표', '공매도', '주가 조작']</t>
+          <t>['보안주', 'AI', '해킹']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
@@ -1222,13 +1222,13 @@
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="H9" t="n">
         <v>25.42</v>
@@ -1254,7 +1254,7 @@
         <v>25.47</v>
       </c>
       <c r="O9" t="n">
-        <v>9524102850</v>
+        <v>9721873170</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>분기 순이익 흑자 전환 및 재무 상태 개선. 목표가 하향 및 증권사 신뢰도 저하.</t>
+          <t>호조의 분기 순이익 및 재무 상태 개선 언급. 공매도 세력에 대한 부정적 시각과 함께 2차 상승 및 신사업 기대감 존재. 무위험 수익 구간 진입 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['순이익', '재무', '목표가']</t>
+          <t>['분기 순이익', '공매도', '신사업 기대']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209500</v>
+        <v>209000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.33%</t>
+          <t>'-2.56%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="G10" t="n">
-        <v>1545</v>
+        <v>1598</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1759332870000</v>
+        <v>1790093134000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 정부의 정책에 대한 강한 비판과 시장 혼란 우려. 연기금 매도세 관측.</t>
+          <t>정치적 이슈와 관련된 부정적 언급 다수. 일부 투자자는 매수 구간으로 판단하나, 시장 붕괴 가능성 및 연기금 매도 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['정치적 이슈', '연기금 매도', '매수 구간']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16560</v>
+        <v>16540</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.39%</t>
+          <t>'-4.50%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>20605014935</v>
+        <v>21111717880</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58500</v>
+        <v>58400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-5.19%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G12" t="n">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>81413184850</v>
+        <v>83088770050</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9120</v>
+        <v>9080</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.61%</t>
+          <t>'-10.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F13" t="n">
         <v>67</v>
       </c>
       <c r="G13" t="n">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>40385889170</v>
+        <v>40766187960</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 하락세 지속 및 횡보 예상, 투자주의 종목 관련 언급.</t>
+          <t>하락 추세에 대한 부정적 전망 다수. 야금야금 털고 있다는 의견과 함께 하한가 예상 등 급격한 하락 가능성 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 하락', '횡보', '투자주의']</t>
+          <t>['하락 추세', '하한가 예상', '조정 및 횡보']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_12.xlsx
+++ b/data/trending_integrated_20261023_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4262</v>
+        <v>4215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+13.65%</t>
+          <t>'+12.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="F2" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G2" t="n">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>135354138492</v>
+        <v>136212339175</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60300</v>
+        <v>60400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.84%</t>
+          <t>'+9.03%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F3" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G3" t="n">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>542269234600</v>
+        <v>546333511200</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외국인 및 기관 매수세 유입, 자사주 매입/소각 공시, MSCI 편입 기대감으로 인한 상승 전망. 중동 특수 및 과거 주가 흐름 기반 목표가 제시.</t>
+          <t>외인·기관 대규모 순매수와 자사주 매입 소각 기대감, MSCI 패시브 자금 유입 전망. 목표 주가 상향 및 중장기 상승 추세 예상.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI 편입', '중동 특수']</t>
+          <t>['자사주 매입', 'MSCI 패시브', '추세 전환']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1222000</v>
+        <v>1224000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.08%</t>
+          <t>'+0.08%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -765,10 +765,10 @@
         <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G4" t="n">
-        <v>1307</v>
+        <v>1345</v>
       </c>
       <c r="H4" t="n">
         <v>48.77</v>
@@ -794,7 +794,7 @@
         <v>48.79</v>
       </c>
       <c r="O4" t="n">
-        <v>2365660076000</v>
+        <v>2392556373000</v>
       </c>
       <c r="P4" t="n">
         <v>2987000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>매도 의견과 함께 부정적 언급이 많으나, 주주환원 발표 기대감 및 일부 투자자의 매수 의견 존재. 나스닥 반도체 하락 영향 언급.</t>
+          <t>IPO 중단 및 반도체 시장 하락 영향. 주가 부양 및 주주환원 정책에 대한 기대감 상존.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['주주환원', '매도 의견', '나스닥 하락']</t>
+          <t>['IPO 중단', '주주환원', '반도체 하락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8650</v>
+        <v>8670</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.04</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F5" t="n">
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H5" t="n">
         <v>5.11</v>
@@ -886,7 +886,7 @@
         <v>5.15</v>
       </c>
       <c r="O5" t="n">
-        <v>6243927810</v>
+        <v>6295406910</v>
       </c>
       <c r="P5" t="n">
         <v>15900</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13250</v>
+        <v>13260</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.60%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="H6" t="n">
         <v>2.92</v>
@@ -978,7 +978,7 @@
         <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>52340364325</v>
+        <v>52764290410</v>
       </c>
       <c r="P6" t="n">
         <v>31500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14380</v>
+        <v>14410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.03%</t>
+          <t>'-0.83%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
         <v>34</v>
       </c>
       <c r="G7" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>22081255820</v>
+        <v>22368761990</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17020</v>
+        <v>17130</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.90%</t>
+          <t>'-1.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.48</v>
       </c>
       <c r="E8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="H8" t="n">
         <v>3.77</v>
@@ -1162,7 +1162,7 @@
         <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>46510245965</v>
+        <v>46590992185</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>미국 보안주 폭등 속 라온시큐어 주가 변동성. AI 보안 해킹 우려.</t>
+          <t>보안주 섹터의 개별 이슈 및 국내외 시장 상황에 따른 변동성 확대. 재매수 시점 접근 및 종목별 이슈 주목.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI', '해킹']</t>
+          <t>['보안주', 'AI 해킹', '변동성']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7080</v>
+        <v>7070</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.07%</t>
+          <t>'-2.21%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="H9" t="n">
         <v>25.42</v>
@@ -1254,7 +1254,7 @@
         <v>25.47</v>
       </c>
       <c r="O9" t="n">
-        <v>9721873170</v>
+        <v>9894972610</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>호조의 분기 순이익 및 재무 상태 개선 언급. 공매도 세력에 대한 부정적 시각과 함께 2차 상승 및 신사업 기대감 존재. 무위험 수익 구간 진입 언급.</t>
+          <t>견조한 순이익 발표에도 불구하고 목표가 하향 조정. 외인·기관 순매수 유입 및 무위험 수익 구간 진입 가능성 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['분기 순이익', '공매도', '신사업 기대']</t>
+          <t>['순이익 개선', '목표가 하향', '외인 순매수']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="G10" t="n">
-        <v>1598</v>
+        <v>1605</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1790093134000</v>
+        <v>1815030772000</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈와 관련된 부정적 언급 다수. 일부 투자자는 매수 구간으로 판단하나, 시장 붕괴 가능성 및 연기금 매도 언급.</t>
+          <t>정치적 이슈에 따른 시장 불안감 확산. 반도체 섹터 전반의 하락세와 연기금 매도세 지속.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치적 이슈', '연기금 매도', '매수 구간']</t>
+          <t>['시장 붕괴', '정치적 불안', '연기금 매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16540</v>
+        <v>16550</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.50%</t>
+          <t>'-4.45%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>21111717880</v>
+        <v>21490210850</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 하락 및 정치 관련 부정적 언급, 조선주 전반의 약세 언급.</t>
+          <t>조선업 섹터 전반의 하락세와 신저점 갱신. 주주환원 정책 발표 가능성 언급 및 주가 부양 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가 하락', '정치', '조선주']</t>
+          <t>['조선업 하락', '신저점', '주주환원']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58400</v>
+        <v>58500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.19%</t>
+          <t>'-5.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G12" t="n">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>83088770050</v>
+        <v>84918556200</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9080</v>
+        <v>9120</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-10.01%</t>
+          <t>'-9.61%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F13" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>40766187960</v>
+        <v>41108331280</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>하락 추세에 대한 부정적 전망 다수. 야금야금 털고 있다는 의견과 함께 하한가 예상 등 급격한 하락 가능성 언급.</t>
+          <t>급락세 지속 및 하한가 기록. 단기 조정 및 횡보 예상, 매수 관망세.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['하락 추세', '하한가 예상', '조정 및 횡보']</t>
+          <t>['급락', '하한가', '관망세']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_12.xlsx
+++ b/data/trending_integrated_20261023_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4215</v>
+        <v>4180</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+12.40%</t>
+          <t>'+11.47%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F2" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G2" t="n">
-        <v>519</v>
+        <v>542</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>136212339175</v>
+        <v>137798316356</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각으로 인한 방산주 동반 상승 기대. 미국 시장 급등 및 코브라볼 평택 포착 등 뉴스 기반 분석.</t>
+          <t>북한 관련 지정학적 리스크 부각 및 방산주 강세. 미국 증시 폭락 속 록히드마틴 급등 영향. 김정은 관련 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '방산주', '코브라볼']</t>
+          <t>['지정학적 리스크', '방산주', '록히드마틴']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F3" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G3" t="n">
-        <v>913</v>
+        <v>929</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>546333511200</v>
+        <v>550567113700</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 대규모 순매수와 자사주 매입 소각 기대감, MSCI 패시브 자금 유입 전망. 목표 주가 상향 및 중장기 상승 추세 예상.</t>
+          <t>외인/기관 대규모 순매수 및 자사주 매입/소각 공시 기반 주가 방어 기대. MSCI 패시브 자금 유입 및 중동 특수 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI 패시브', '추세 전환']</t>
+          <t>['자사주 매입', ' MSCI 패시브', '중동 특수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1224000</v>
+        <v>13430</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.08%</t>
+          <t>'+0.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>492</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>1345</v>
+        <v>384</v>
       </c>
       <c r="H4" t="n">
-        <v>48.77</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1223000</v>
+        <v>13340</v>
       </c>
       <c r="K4" t="n">
-        <v>1200000</v>
+        <v>12840</v>
       </c>
       <c r="L4" t="n">
-        <v>1237000</v>
+        <v>13700</v>
       </c>
       <c r="M4" t="n">
-        <v>1171000</v>
+        <v>12530</v>
       </c>
       <c r="N4" t="n">
-        <v>48.79</v>
+        <v>3.48</v>
       </c>
       <c r="O4" t="n">
-        <v>2392556373000</v>
+        <v>53463385710</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>1640</v>
       </c>
       <c r="R4" t="n">
-        <v>-339000</v>
+        <v>-159000</v>
       </c>
       <c r="S4" t="n">
-        <v>94000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>IPO 중단 및 반도체 시장 하락 영향. 주가 부양 및 주주환원 정책에 대한 기대감 상존.</t>
+          <t>유리기판 기술력 기반 EUV 반도체 대장주 부각. 삼성 인수설 및 SK하이닉스 양전 영향. 외인 순매수.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['IPO 중단', '주주환원', '반도체 하락']</t>
+          <t>['유리기판', 'EUV 반도체', '삼성 인수설']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8670</v>
+        <v>1230000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>101</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>500</v>
       </c>
       <c r="G5" t="n">
-        <v>183</v>
+        <v>1350</v>
       </c>
       <c r="H5" t="n">
-        <v>5.11</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8680</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>9410</v>
+        <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>9460</v>
+        <v>1237000</v>
       </c>
       <c r="M5" t="n">
-        <v>8640</v>
+        <v>1171000</v>
       </c>
       <c r="N5" t="n">
-        <v>5.15</v>
+        <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>6295406910</v>
+        <v>2450881453000</v>
       </c>
       <c r="P5" t="n">
-        <v>15900</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6310</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-311000</v>
+        <v>-339000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
+          <t>국민연금 운용 및 호남 반도체 사업 관련 부정적 언급. IPO 중단 및 투자 위험 경고. 개인 투자자 대상 매수 권유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
+          <t>['국민연금', '호남 반도체', 'IPO 중단']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13260</v>
+        <v>8680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.60%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>379</v>
+        <v>185</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>5.11</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>13340</v>
+        <v>8680</v>
       </c>
       <c r="K6" t="n">
-        <v>12840</v>
+        <v>9410</v>
       </c>
       <c r="L6" t="n">
-        <v>13700</v>
+        <v>9460</v>
       </c>
       <c r="M6" t="n">
-        <v>12530</v>
+        <v>8640</v>
       </c>
       <c r="N6" t="n">
-        <v>3.48</v>
+        <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>52764290410</v>
+        <v>6317888970</v>
       </c>
       <c r="P6" t="n">
-        <v>31500</v>
+        <v>15900</v>
       </c>
       <c r="Q6" t="n">
-        <v>1640</v>
+        <v>6310</v>
       </c>
       <c r="R6" t="n">
-        <v>-159000</v>
+        <v>-311000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>유리기판 관련 기술성 부각 및 삼성 인수설 기반 긍정적 전망. 외인 매수세 유입 및 SK하이닉스 반등에 따른 상승 기대.</t>
+          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['유리기판', '삼성 인수설', '외인 매수']</t>
+          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14410</v>
+        <v>14460</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.83%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
         <v>9.890000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>22368761990</v>
+        <v>22687634670</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>실적 발표 이후 주가 하락세 지속, 공매도 및 주가 조작 의혹 제기, 대차 해지 동참 요구.</t>
+          <t>이재명 대통령의 주가 조작 방관 비판. 3분기 실적 및 대차 해지 독려. 거래량 부족으로 인한 하락세 진정 및 주말 호재 기대.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['실적 발표', '공매도', '주가 조작']</t>
+          <t>['주가 조작', '3분기 실적', '대차 해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17130</v>
+        <v>17190</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.27%</t>
+          <t>'-0.92%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>3.29</v>
       </c>
       <c r="O8" t="n">
-        <v>46590992185</v>
+        <v>46717441505</v>
       </c>
       <c r="P8" t="n">
         <v>22450</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7070</v>
+        <v>7100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.21%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="H9" t="n">
         <v>25.42</v>
@@ -1254,7 +1254,7 @@
         <v>25.47</v>
       </c>
       <c r="O9" t="n">
-        <v>9894972610</v>
+        <v>10047548760</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>견조한 순이익 발표에도 불구하고 목표가 하향 조정. 외인·기관 순매수 유입 및 무위험 수익 구간 진입 가능성 언급.</t>
+          <t>3분기 순이익 7,556억으로 컨센서스 상회, 재무 상태 개선. 외인/기관 순매수 및 배당 기대. FLiPP 기반 주가 재평가 가능성.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['순이익 개선', '목표가 하향', '외인 순매수']</t>
+          <t>['분기 순이익', '재무 개선', 'FLiPP']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>209000</v>
+        <v>210500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.56%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="G10" t="n">
-        <v>1605</v>
+        <v>1556</v>
       </c>
       <c r="H10" t="n">
         <v>46.13</v>
@@ -1346,7 +1346,7 @@
         <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>1815030772000</v>
+        <v>1860894069500</v>
       </c>
       <c r="P10" t="n">
         <v>374500</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈에 따른 시장 불안감 확산. 반도체 섹터 전반의 하락세와 연기금 매도세 지속.</t>
+          <t>이재명 정부 정책 및 시장 교란에 대한 부정적 언급. 연기금 매도 및 시장 붕괴 우려. 나스닥/필라델피아 반도체 지수 상승 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['시장 붕괴', '정치적 불안', '연기금 매도']</t>
+          <t>['시장 교란', '연기금 매도', '반도체 지수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16550</v>
+        <v>16590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.45%</t>
+          <t>'-4.21%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F11" t="n">
         <v>63</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>21490210850</v>
+        <v>22108390120</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58500</v>
+        <v>58700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.03%</t>
+          <t>'-4.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F12" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G12" t="n">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>84918556200</v>
+        <v>86803027200</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9120</v>
+        <v>9135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.61%</t>
+          <t>'-9.46%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F13" t="n">
         <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>41108331280</v>
+        <v>41480720250</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>

--- a/data/trending_integrated_20261023_12.xlsx
+++ b/data/trending_integrated_20261023_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4180</v>
+        <v>4145</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+11.47%</t>
+          <t>'+10.53%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F2" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G2" t="n">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>137798316356</v>
+        <v>139011102050</v>
       </c>
       <c r="P2" t="n">
         <v>7050</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각 및 방산주 강세. 미국 증시 폭락 속 록히드마틴 급등 영향. 김정은 관련 언급.</t>
+          <t>북한 관련 지정학적 리스크 부각 및 미군 특수정찰기 포착에 따른 방산주 동반 급등세. 록히드마틴 급등 사례 언급하며 투자 심리 자극.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '방산주', '록히드마틴']</t>
+          <t>['지정학적 리스크', '방산주', '특수정찰기']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60400</v>
+        <v>60700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.03%</t>
+          <t>'+9.57%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F3" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G3" t="n">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>550567113700</v>
+        <v>557222863350</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인/기관 대규모 순매수 및 자사주 매입/소각 공시 기반 주가 방어 기대. MSCI 패시브 자금 유입 및 중동 특수 기대.</t>
+          <t>외인·기관 매수세 유입 및 자사주 매입·소각 공시 기반 주가 방어 기대. MSCI 패시브 자금 유입 및 중동 특수 통한 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', ' MSCI 패시브', '중동 특수']</t>
+          <t>['자사주 매입', 'MSCI 패시브', '중동 특수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13430</v>
+        <v>1237000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.67%</t>
+          <t>'+1.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>505</v>
       </c>
       <c r="G4" t="n">
-        <v>384</v>
+        <v>1358</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>48.77</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>13340</v>
+        <v>1223000</v>
       </c>
       <c r="K4" t="n">
-        <v>12840</v>
+        <v>1200000</v>
       </c>
       <c r="L4" t="n">
-        <v>13700</v>
+        <v>1241000</v>
       </c>
       <c r="M4" t="n">
-        <v>12530</v>
+        <v>1171000</v>
       </c>
       <c r="N4" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="O4" t="n">
-        <v>53463385710</v>
+        <v>2537199621500</v>
       </c>
       <c r="P4" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R4" t="n">
-        <v>-159000</v>
+        <v>-339000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유리기판 기술력 기반 EUV 반도체 대장주 부각. 삼성 인수설 및 SK하이닉스 양전 영향. 외인 순매수.</t>
+          <t>정치적 이슈 및 지역 투자 논란으로 인한 부정적 전망 속에, 개인 투자자 대상 매물 소화 및 IPO 중단 관련 언급. 적정주가 및 기대치 언급 있으나 실체적 근거는 미흡.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유리기판', 'EUV 반도체', '삼성 인수설']</t>
+          <t>['호남 반도체', 'IPO 중단', '적정주가']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1230000</v>
+        <v>13420</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+0.60%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>1350</v>
+        <v>389</v>
       </c>
       <c r="H5" t="n">
-        <v>48.77</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1223000</v>
+        <v>13340</v>
       </c>
       <c r="K5" t="n">
-        <v>1200000</v>
+        <v>12840</v>
       </c>
       <c r="L5" t="n">
-        <v>1237000</v>
+        <v>13700</v>
       </c>
       <c r="M5" t="n">
-        <v>1171000</v>
+        <v>12530</v>
       </c>
       <c r="N5" t="n">
-        <v>48.79</v>
+        <v>3.48</v>
       </c>
       <c r="O5" t="n">
-        <v>2450881453000</v>
+        <v>55200719965</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>31500</v>
       </c>
       <c r="Q5" t="n">
-        <v>468000</v>
+        <v>1640</v>
       </c>
       <c r="R5" t="n">
-        <v>-339000</v>
+        <v>-159000</v>
       </c>
       <c r="S5" t="n">
-        <v>94000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국민연금 운용 및 호남 반도체 사업 관련 부정적 언급. IPO 중단 및 투자 위험 경고. 개인 투자자 대상 매수 권유.</t>
+          <t>유리기판 기술력에 대한 기대감과 함께 삼성 인수설, EUV 반도체 특허 언급. 외인 매수세 유입 및 광섬유 품귀 현상 부각으로 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['국민연금', '호남 반도체', 'IPO 중단']</t>
+          <t>['유리기판', 'EUV', '삼성 인수설']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8680</v>
+        <v>8710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.04</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H6" t="n">
         <v>5.11</v>
@@ -978,7 +978,7 @@
         <v>5.15</v>
       </c>
       <c r="O6" t="n">
-        <v>6317888970</v>
+        <v>6364464450</v>
       </c>
       <c r="P6" t="n">
         <v>15900</v>
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14460</v>
+        <v>17360</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'+0.06%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.06</v>
+        <v>0.48</v>
       </c>
       <c r="E7" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="H7" t="n">
-        <v>9.890000000000001</v>
+        <v>3.77</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14530</v>
+        <v>17350</v>
       </c>
       <c r="K7" t="n">
-        <v>14190</v>
+        <v>18130</v>
       </c>
       <c r="L7" t="n">
-        <v>14710</v>
+        <v>19070</v>
       </c>
       <c r="M7" t="n">
-        <v>13810</v>
+        <v>16530</v>
       </c>
       <c r="N7" t="n">
-        <v>9.949999999999999</v>
+        <v>3.29</v>
       </c>
       <c r="O7" t="n">
-        <v>22687634670</v>
+        <v>47584642475</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>22450</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>6320</v>
       </c>
       <c r="R7" t="n">
-        <v>-96000</v>
+        <v>-11000</v>
       </c>
       <c r="S7" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 대통령의 주가 조작 방관 비판. 3분기 실적 및 대차 해지 독려. 거래량 부족으로 인한 하락세 진정 및 주말 호재 기대.</t>
+          <t>보안주 섹터의 개별 이슈 및 국내외 시장 상황에 따른 변동성 확대. 재매수 시점 접근 및 종목별 이슈 주목.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 조작', '3분기 실적', '대차 해지']</t>
+          <t>['보안주', 'AI 해킹', '변동성']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17190</v>
+        <v>14470</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.92%</t>
+          <t>'-0.41%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.48</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="H8" t="n">
-        <v>3.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>17350</v>
+        <v>14530</v>
       </c>
       <c r="K8" t="n">
-        <v>18130</v>
+        <v>14190</v>
       </c>
       <c r="L8" t="n">
-        <v>19070</v>
+        <v>14710</v>
       </c>
       <c r="M8" t="n">
-        <v>16530</v>
+        <v>13810</v>
       </c>
       <c r="N8" t="n">
-        <v>3.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>46717441505</v>
+        <v>23105536330</v>
       </c>
       <c r="P8" t="n">
-        <v>22450</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>6320</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-11000</v>
+        <v>-96000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>보안주 섹터의 개별 이슈 및 국내외 시장 상황에 따른 변동성 확대. 재매수 시점 접근 및 종목별 이슈 주목.</t>
+          <t>이재명 대통령의 주가 조작 방관 비판. 3분기 실적 및 대차 해지 독려. 거래량 부족으로 인한 하락세 진정 및 주말 호재 기대.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['보안주', 'AI 해킹', '변동성']</t>
+          <t>['주가 조작', '3분기 실적', '대차 해지']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7100</v>
+        <v>211000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="G9" t="n">
-        <v>378</v>
+        <v>1542</v>
       </c>
       <c r="H9" t="n">
-        <v>25.42</v>
+        <v>46.13</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>7230</v>
+        <v>214500</v>
       </c>
       <c r="K9" t="n">
-        <v>7100</v>
+        <v>206000</v>
       </c>
       <c r="L9" t="n">
-        <v>7220</v>
+        <v>212000</v>
       </c>
       <c r="M9" t="n">
-        <v>7010</v>
+        <v>203500</v>
       </c>
       <c r="N9" t="n">
-        <v>25.47</v>
+        <v>46.14</v>
       </c>
       <c r="O9" t="n">
-        <v>10047548760</v>
+        <v>1923339339750</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>7010</v>
+        <v>94500</v>
       </c>
       <c r="R9" t="n">
-        <v>-54000</v>
+        <v>-358000</v>
       </c>
       <c r="S9" t="n">
-        <v>13000</v>
+        <v>82000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3분기 순이익 7,556억으로 컨센서스 상회, 재무 상태 개선. 외인/기관 순매수 및 배당 기대. FLiPP 기반 주가 재평가 가능성.</t>
+          <t>정치적 이슈로 인한 시장 전반의 불안감 속에서 반도체 섹터 일부 상승 기대와 함께, 연기금 매도세 및 시장 붕괴 가능성 우려. 자사주 소각 이벤트 주목.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['분기 순이익', '재무 개선', 'FLiPP']</t>
+          <t>['연기금', '자사주 소각', '시장 붕괴']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>210500</v>
+        <v>7100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>129</v>
       </c>
       <c r="F10" t="n">
-        <v>507</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>1556</v>
+        <v>385</v>
       </c>
       <c r="H10" t="n">
-        <v>46.13</v>
+        <v>25.42</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>214500</v>
+        <v>7230</v>
       </c>
       <c r="K10" t="n">
-        <v>206000</v>
+        <v>7100</v>
       </c>
       <c r="L10" t="n">
-        <v>212000</v>
+        <v>7220</v>
       </c>
       <c r="M10" t="n">
-        <v>203500</v>
+        <v>7010</v>
       </c>
       <c r="N10" t="n">
-        <v>46.14</v>
+        <v>25.47</v>
       </c>
       <c r="O10" t="n">
-        <v>1860894069500</v>
+        <v>10287587795</v>
       </c>
       <c r="P10" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>94500</v>
+        <v>7010</v>
       </c>
       <c r="R10" t="n">
-        <v>-358000</v>
+        <v>-54000</v>
       </c>
       <c r="S10" t="n">
-        <v>82000</v>
+        <v>13000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>이재명 정부 정책 및 시장 교란에 대한 부정적 언급. 연기금 매도 및 시장 붕괴 우려. 나스닥/필라델피아 반도체 지수 상승 기대.</t>
+          <t>3분기 순이익 7,556억으로 컨센서스 상회, 재무 상태 개선. 외인/기관 순매수 및 배당 기대. FLiPP 기반 주가 재평가 가능성.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['시장 교란', '연기금 매도', '반도체 지수']</t>
+          <t>['분기 순이익', '재무 개선', 'FLiPP']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16590</v>
+        <v>16580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.21%</t>
+          <t>'-4.27%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>63</v>
       </c>
       <c r="G11" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H11" t="n">
         <v>27.89</v>
@@ -1438,7 +1438,7 @@
         <v>27.87</v>
       </c>
       <c r="O11" t="n">
-        <v>22108390120</v>
+        <v>22840839990</v>
       </c>
       <c r="P11" t="n">
         <v>35350</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58700</v>
+        <v>58800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.71%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F12" t="n">
         <v>150</v>
       </c>
       <c r="G12" t="n">
-        <v>602</v>
+        <v>615</v>
       </c>
       <c r="H12" t="n">
         <v>22.25</v>
@@ -1530,7 +1530,7 @@
         <v>22.26</v>
       </c>
       <c r="O12" t="n">
-        <v>86803027200</v>
+        <v>89877755150</v>
       </c>
       <c r="P12" t="n">
         <v>139200</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9135</v>
+        <v>9160</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.46%</t>
+          <t>'-9.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-1.19</v>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H13" t="n">
         <v>2.5</v>
@@ -1622,7 +1622,7 @@
         <v>3.69</v>
       </c>
       <c r="O13" t="n">
-        <v>41480720250</v>
+        <v>42419089135</v>
       </c>
       <c r="P13" t="n">
         <v>11690</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>급락세 지속 및 하한가 기록. 단기 조정 및 횡보 예상, 매수 관망세.</t>
+          <t>수출 관련 긍정적 뉴스 언급에도 불구하고, 차트상 하락 추세 및 투자 심리 악화로 인한 조정 및 횡보 예상. 대규모 급락 가능성 및 관망세 짙어짐.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['급락', '하한가', '관망세']</t>
+          <t>['수출', '조정', '횡보']</t>
         </is>
       </c>
       <c r="X13" t="n">

--- a/data/trending_integrated_20261023_12.xlsx
+++ b/data/trending_integrated_20261023_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z13"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>빅텍</t>
+          <t>앤로보틱스</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4145</v>
+        <v>1950</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+10.53%</t>
+          <t>'+19.27%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="E2" t="n">
-        <v>270</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>545</v>
+        <v>141</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,51 +595,51 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3750</v>
+        <v>1635</v>
       </c>
       <c r="K2" t="n">
-        <v>3905</v>
+        <v>1600</v>
       </c>
       <c r="L2" t="n">
-        <v>4550</v>
+        <v>1968</v>
       </c>
       <c r="M2" t="n">
-        <v>3815</v>
+        <v>1538</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="O2" t="n">
-        <v>139011102050</v>
+        <v>50790857315</v>
       </c>
       <c r="P2" t="n">
-        <v>7050</v>
+        <v>4980</v>
       </c>
       <c r="Q2" t="n">
-        <v>2500</v>
+        <v>735</v>
       </c>
       <c r="R2" t="n">
-        <v>-250000</v>
+        <v>85000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>북한 관련 지정학적 리스크 부각 및 미군 특수정찰기 포착에 따른 방산주 동반 급등세. 록히드마틴 급등 사례 언급하며 투자 심리 자극.</t>
+          <t>로봇주 및 휴머노이드 관련 긍정적 전망. 외인 매수세 유입 및 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['지정학적 리스크', '방산주', '특수정찰기']</t>
+          <t>['로봇주', '휴머노이드', '외인 매수']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>065450</t>
+          <t>138360</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60700</v>
+        <v>60600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+9.57%</t>
+          <t>'+9.39%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="F3" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G3" t="n">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="H3" t="n">
         <v>38.9</v>
@@ -702,7 +702,7 @@
         <v>37.72</v>
       </c>
       <c r="O3" t="n">
-        <v>557222863350</v>
+        <v>562931783650</v>
       </c>
       <c r="P3" t="n">
         <v>67300</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>외인·기관 매수세 유입 및 자사주 매입·소각 공시 기반 주가 방어 기대. MSCI 패시브 자금 유입 및 중동 특수 통한 추가 상승 전망.</t>
+          <t>외인·기관 매수세 유입 및 자사주 매입/소각 공시 기반 주가 상승 전망. MSCI 편입 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['자사주 매입', 'MSCI 패시브', '중동 특수']</t>
+          <t>['자사주 매입', 'MSCI 편입', '외인 수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,83 +747,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>빅텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1237000</v>
+        <v>4070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.14%</t>
+          <t>'+8.53%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>800</v>
+        <v>271</v>
       </c>
       <c r="F4" t="n">
-        <v>505</v>
+        <v>146</v>
       </c>
       <c r="G4" t="n">
-        <v>1358</v>
+        <v>560</v>
       </c>
       <c r="H4" t="n">
-        <v>48.77</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1223000</v>
+        <v>3750</v>
       </c>
       <c r="K4" t="n">
-        <v>1200000</v>
+        <v>3905</v>
       </c>
       <c r="L4" t="n">
-        <v>1241000</v>
+        <v>4550</v>
       </c>
       <c r="M4" t="n">
-        <v>1171000</v>
+        <v>3815</v>
       </c>
       <c r="N4" t="n">
-        <v>48.79</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2537199621500</v>
+        <v>140578068670</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>7050</v>
       </c>
       <c r="Q4" t="n">
-        <v>468000</v>
+        <v>2500</v>
       </c>
       <c r="R4" t="n">
-        <v>-339000</v>
+        <v>-250000</v>
       </c>
       <c r="S4" t="n">
-        <v>94000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 지역 투자 논란으로 인한 부정적 전망 속에, 개인 투자자 대상 매물 소화 및 IPO 중단 관련 언급. 적정주가 및 기대치 언급 있으나 실체적 근거는 미흡.</t>
+          <t>북한 관련 지정학적 이슈와 방산주 상승 연관성 언급. 외인 매도 및 주가 조작 의혹도 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['호남 반도체', 'IPO 중단', '적정주가']</t>
+          <t>['북한 이슈', '방산주', '지정학적']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>065450</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13420</v>
+        <v>1249000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+2.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>89</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>515</v>
       </c>
       <c r="G5" t="n">
-        <v>389</v>
+        <v>1397</v>
       </c>
       <c r="H5" t="n">
-        <v>2.92</v>
+        <v>48.77</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13340</v>
+        <v>1223000</v>
       </c>
       <c r="K5" t="n">
-        <v>12840</v>
+        <v>1200000</v>
       </c>
       <c r="L5" t="n">
-        <v>13700</v>
+        <v>1250000</v>
       </c>
       <c r="M5" t="n">
-        <v>12530</v>
+        <v>1171000</v>
       </c>
       <c r="N5" t="n">
-        <v>3.48</v>
+        <v>48.79</v>
       </c>
       <c r="O5" t="n">
-        <v>55200719965</v>
+        <v>2628913950500</v>
       </c>
       <c r="P5" t="n">
-        <v>31500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1640</v>
+        <v>468000</v>
       </c>
       <c r="R5" t="n">
-        <v>-159000</v>
+        <v>-339000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>유리기판 기술력에 대한 기대감과 함께 삼성 인수설, EUV 반도체 특허 언급. 외인 매수세 유입 및 광섬유 품귀 현상 부각으로 긍정적 전망 제시.</t>
+          <t>정치적 이슈와 연계된 부정적 언급 다수. 일부 긍정적 전망이나 전반적인 불안감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유리기판', 'EUV', '삼성 인수설']</t>
+          <t>['정치적 이슈', '반도체', '적정주가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8710</v>
+        <v>13465</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.04</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>189</v>
+        <v>413</v>
       </c>
       <c r="H6" t="n">
-        <v>5.11</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>8680</v>
+        <v>13340</v>
       </c>
       <c r="K6" t="n">
-        <v>9410</v>
+        <v>12840</v>
       </c>
       <c r="L6" t="n">
-        <v>9460</v>
+        <v>13700</v>
       </c>
       <c r="M6" t="n">
-        <v>8640</v>
+        <v>12530</v>
       </c>
       <c r="N6" t="n">
-        <v>5.15</v>
+        <v>3.48</v>
       </c>
       <c r="O6" t="n">
-        <v>6364464450</v>
+        <v>56187040730</v>
       </c>
       <c r="P6" t="n">
-        <v>15900</v>
+        <v>31500</v>
       </c>
       <c r="Q6" t="n">
-        <v>6310</v>
+        <v>1640</v>
       </c>
       <c r="R6" t="n">
-        <v>-311000</v>
+        <v>-159000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>해외 특허에도 불구하고 주가 부양 미흡, 일부 투자자들의 비판과 함께 단타 매매 언급. 허풍제약이라는 부정적 별칭 등장.</t>
+          <t>유리기판 기술력 및 삼성 인수설 관련 긍정적 언급. 광섬유 품귀 현상도 거론.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뇌졸증 치료제', '단주거래', '신약개발']</t>
+          <t>['유리기판', '삼성 인수설', '광섬유']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>019170</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>신풍제약</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17360</v>
+        <v>8690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.06%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="H7" t="n">
-        <v>3.77</v>
+        <v>5.11</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>17350</v>
+        <v>8680</v>
       </c>
       <c r="K7" t="n">
-        <v>18130</v>
+        <v>9410</v>
       </c>
       <c r="L7" t="n">
-        <v>19070</v>
+        <v>9460</v>
       </c>
       <c r="M7" t="n">
-        <v>16530</v>
+        <v>8640</v>
       </c>
       <c r="N7" t="n">
-        <v>3.29</v>
+        <v>5.15</v>
       </c>
       <c r="O7" t="n">
-        <v>47584642475</v>
+        <v>6381107230</v>
       </c>
       <c r="P7" t="n">
-        <v>22450</v>
+        <v>15900</v>
       </c>
       <c r="Q7" t="n">
-        <v>6320</v>
+        <v>6310</v>
       </c>
       <c r="R7" t="n">
-        <v>-11000</v>
+        <v>-311000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>보안주 섹터의 개별 이슈 및 국내외 시장 상황에 따른 변동성 확대. 재매수 시점 접근 및 종목별 이슈 주목.</t>
+          <t>신풍제약에 대한 부정적인 의견이 지배적이며, 근거 없는 기대감과 개인 투자자들의 손실 경험이 언급되었습니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['보안주', 'AI 해킹', '변동성']</t>
+          <t>['신약', '치료제', '특허']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>019170</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14470</v>
+        <v>14510</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.41%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H8" t="n">
         <v>9.890000000000001</v>
@@ -1162,7 +1162,7 @@
         <v>9.949999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>23105536330</v>
+        <v>23533594450</v>
       </c>
       <c r="P8" t="n">
         <v>40350</v>
@@ -1207,83 +1207,83 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211000</v>
+        <v>17250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-0.58%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>0.48</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>83</v>
       </c>
       <c r="F9" t="n">
-        <v>500</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>1542</v>
+        <v>142</v>
       </c>
       <c r="H9" t="n">
-        <v>46.13</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>214500</v>
+        <v>17350</v>
       </c>
       <c r="K9" t="n">
-        <v>206000</v>
+        <v>18130</v>
       </c>
       <c r="L9" t="n">
-        <v>212000</v>
+        <v>19070</v>
       </c>
       <c r="M9" t="n">
-        <v>203500</v>
+        <v>16530</v>
       </c>
       <c r="N9" t="n">
-        <v>46.14</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>1923339339750</v>
+        <v>47927892350</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>22450</v>
       </c>
       <c r="Q9" t="n">
-        <v>94500</v>
+        <v>6320</v>
       </c>
       <c r="R9" t="n">
-        <v>-358000</v>
+        <v>-11000</v>
       </c>
       <c r="S9" t="n">
-        <v>82000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>정치적 이슈로 인한 시장 전반의 불안감 속에서 반도체 섹터 일부 상승 기대와 함께, 연기금 매도세 및 시장 붕괴 가능성 우려. 자사주 소각 이벤트 주목.</t>
+          <t>보안주 상승 및 AI 관련 긍정적 뉴스 언급. 주가 조작 및 최악의 무빙에 대한 불만도 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['연기금', '자사주 소각', '시장 붕괴']</t>
+          <t>['보안주', 'AI', '주가 조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7100</v>
+        <v>212000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'-1.17%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>129</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>59</v>
+        <v>499</v>
       </c>
       <c r="G10" t="n">
-        <v>385</v>
+        <v>1559</v>
       </c>
       <c r="H10" t="n">
-        <v>25.42</v>
+        <v>46.13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>7230</v>
+        <v>214500</v>
       </c>
       <c r="K10" t="n">
-        <v>7100</v>
+        <v>206000</v>
       </c>
       <c r="L10" t="n">
-        <v>7220</v>
+        <v>213500</v>
       </c>
       <c r="M10" t="n">
-        <v>7010</v>
+        <v>203500</v>
       </c>
       <c r="N10" t="n">
-        <v>25.47</v>
+        <v>46.14</v>
       </c>
       <c r="O10" t="n">
-        <v>10287587795</v>
+        <v>2005706506500</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>7010</v>
+        <v>94500</v>
       </c>
       <c r="R10" t="n">
-        <v>-54000</v>
+        <v>-358000</v>
       </c>
       <c r="S10" t="n">
-        <v>13000</v>
+        <v>82000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3분기 순이익 7,556억으로 컨센서스 상회, 재무 상태 개선. 외인/기관 순매수 및 배당 기대. FLiPP 기반 주가 재평가 가능성.</t>
+          <t>정치적 이슈와 경제 시장 붕괴 가능성 언급. 일부 긍정적 지표 있으나 전반적으로 부정적 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['분기 순이익', '재무 개선', 'FLiPP']</t>
+          <t>['시장 붕괴', '정치적 이슈', '매수 구간']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16580</v>
+        <v>7110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.27%</t>
+          <t>'-1.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>205</v>
+        <v>394</v>
       </c>
       <c r="H11" t="n">
-        <v>27.89</v>
+        <v>25.42</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17320</v>
+        <v>7230</v>
       </c>
       <c r="K11" t="n">
-        <v>16810</v>
+        <v>7100</v>
       </c>
       <c r="L11" t="n">
-        <v>16850</v>
+        <v>7220</v>
       </c>
       <c r="M11" t="n">
-        <v>16450</v>
+        <v>7010</v>
       </c>
       <c r="N11" t="n">
-        <v>27.87</v>
+        <v>25.47</v>
       </c>
       <c r="O11" t="n">
-        <v>22840839990</v>
+        <v>10525381405</v>
       </c>
       <c r="P11" t="n">
-        <v>35350</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>16450</v>
+        <v>7010</v>
       </c>
       <c r="R11" t="n">
-        <v>16000</v>
+        <v>-54000</v>
       </c>
       <c r="S11" t="n">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>조선업 섹터 전반의 하락세와 신저점 갱신. 주주환원 정책 발표 가능성 언급 및 주가 부양 기대감.</t>
+          <t>3분기 순이익 7,556억으로 컨센서스 상회, 재무 상태 개선. 외인/기관 순매수 및 배당 기대. FLiPP 기반 주가 재평가 가능성.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['조선업 하락', '신저점', '주주환원']</t>
+          <t>['분기 순이익', '재무 개선', 'FLiPP']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58800</v>
+        <v>16570</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E12" t="n">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="G12" t="n">
-        <v>615</v>
+        <v>216</v>
       </c>
       <c r="H12" t="n">
-        <v>22.25</v>
+        <v>27.89</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>61600</v>
+        <v>17320</v>
       </c>
       <c r="K12" t="n">
-        <v>59600</v>
+        <v>16810</v>
       </c>
       <c r="L12" t="n">
-        <v>60000</v>
+        <v>16850</v>
       </c>
       <c r="M12" t="n">
-        <v>57700</v>
+        <v>16450</v>
       </c>
       <c r="N12" t="n">
-        <v>22.26</v>
+        <v>27.87</v>
       </c>
       <c r="O12" t="n">
-        <v>89877755150</v>
+        <v>23939358035</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>16450</v>
       </c>
       <c r="R12" t="n">
-        <v>-64000</v>
+        <v>16000</v>
       </c>
       <c r="S12" t="n">
-        <v>-100000</v>
+        <v>19000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 증시 폭락 우려와 공매도 물량 부담. 독재당 비판 및 복구 희망.</t>
+          <t>조선주 하락세 및 코스피 하락 관련 부정적 언급. 주주 환원 정책 기대감도 존재.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['공매도', '폭락', '미증시']</t>
+          <t>['조선주', '주주 환원', '코스피']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,97 +1568,189 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9160</v>
+        <v>58800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-9.22%</t>
+          <t>'-4.55%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.19</v>
+        <v>-0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="F13" t="n">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="G13" t="n">
-        <v>342</v>
+        <v>627</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>22.25</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10090</v>
+        <v>61600</v>
       </c>
       <c r="K13" t="n">
-        <v>9770</v>
+        <v>59600</v>
       </c>
       <c r="L13" t="n">
-        <v>10060</v>
+        <v>60000</v>
       </c>
       <c r="M13" t="n">
-        <v>8940</v>
+        <v>57700</v>
       </c>
       <c r="N13" t="n">
-        <v>3.69</v>
+        <v>22.26</v>
       </c>
       <c r="O13" t="n">
-        <v>42419089135</v>
+        <v>91335389800</v>
       </c>
       <c r="P13" t="n">
-        <v>11690</v>
+        <v>139200</v>
       </c>
       <c r="Q13" t="n">
-        <v>2270</v>
+        <v>57000</v>
       </c>
       <c r="R13" t="n">
-        <v>-33000</v>
+        <v>-64000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>-100000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>수출 관련 긍정적 뉴스 언급에도 불구하고, 차트상 하락 추세 및 투자 심리 악화로 인한 조정 및 횡보 예상. 대규모 급락 가능성 및 관망세 짙어짐.</t>
+          <t>정치적 상황과 증시 폭락 우려 언급. 공매도 물량 많다는 분석 존재.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['증시 폭락', '공매도', '정치적 상황']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>034020</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>HT로보틱스</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9280</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-8.03%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>141</v>
+      </c>
+      <c r="F14" t="n">
+        <v>69</v>
+      </c>
+      <c r="G14" t="n">
+        <v>352</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>10090</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9770</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10060</v>
+      </c>
+      <c r="M14" t="n">
+        <v>8940</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="O14" t="n">
+        <v>43103338595</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11690</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2270</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-33000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>주가 하락 및 조정, 횡보 전망. 시장 및 종목 자체에 대한 부정적 분석.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
         <v>0.2</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>['수출', '조정', '횡보']</t>
-        </is>
-      </c>
-      <c r="X13" t="n">
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['하락 전망', '조정', '횡보']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
         <v>6</v>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>396300</t>
         </is>
